--- a/AAII_Financials/Quarterly/ISDAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISDAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="92">
   <si>
     <t>ISDAY</t>
   </si>
@@ -656,71 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -763,8 +769,14 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +819,14 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -851,8 +869,14 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -869,8 +893,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -913,8 +939,14 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -957,8 +989,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1001,8 +1039,14 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1045,8 +1089,14 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1060,8 +1110,10 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1104,8 +1156,14 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1148,8 +1206,14 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1166,8 +1230,10 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1210,8 +1276,14 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1254,8 +1326,14 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1298,8 +1376,14 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1342,8 +1426,14 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1386,8 +1476,14 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1430,8 +1526,14 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1474,8 +1576,14 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1518,8 +1626,14 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1562,8 +1676,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1606,8 +1726,14 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1650,8 +1776,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1694,8 +1826,14 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1738,8 +1876,14 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1782,8 +1926,14 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1826,8 +1976,14 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1870,57 +2026,69 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1937,8 +2105,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1955,140 +2125,160 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16473400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>16858100</v>
+      </c>
+      <c r="F41" s="3">
         <v>18226500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>19792800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>17583800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>13806900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>15668700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>15398000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>12324800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>12474800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>11167400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>14859700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>15038800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>16427000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>18305600</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12386300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>11199800</v>
+      </c>
+      <c r="F42" s="3">
         <v>10323100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>7197300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>8324300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>6440400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>7241000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>5884100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>5049500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>5081500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>7473100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>6185800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>6185000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>5742900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>4282900</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3">
         <v>206100</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>221000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
         <v>316300</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R43" s="3">
         <v>178300</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2131,228 +2321,264 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8030600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>7122900</v>
+      </c>
+      <c r="F45" s="3">
         <v>7360700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>6855100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>6440800</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>6183200</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>134400</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="3">
         <v>90200</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>36890300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>35180700</v>
+      </c>
+      <c r="F46" s="3">
         <v>36463900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>33845200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>32348900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>20247300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>29672200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>21282100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>17374300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>17556300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>19764300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>21045600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>21223800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>22169900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>23220700</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>19759700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>19065300</v>
+      </c>
+      <c r="F47" s="3">
         <v>19989600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>18844800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>18864200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>15758000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>15626700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>15265100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>14188200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>13333700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>14439000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>12095600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>12472100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>12636800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>12216800</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1332300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1277700</v>
+      </c>
+      <c r="F48" s="3">
         <v>1192600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1230700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1209700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1266600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1092400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1244200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1221000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1234600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1154600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1180300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1143000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1122800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1095800</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F49" s="3">
         <v>379900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>5400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>5300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>43000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>326400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>43300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>42800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>43600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>463200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>42500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>43600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>45100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>403300</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2395,8 +2621,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2439,52 +2671,64 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1641400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1583900</v>
+      </c>
+      <c r="F52" s="3">
         <v>263200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1601000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1556100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1728700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>252000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1727100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1699600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1798500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>250700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1675100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1625000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1651300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>252000</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2527,52 +2771,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>162283900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>151114600</v>
+      </c>
+      <c r="F54" s="3">
         <v>149983100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>142679500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>136825200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>116980500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>121532800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>114847300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>106582000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>105660100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>109883700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>104662100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>105502500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>107930900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>107145000</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2589,8 +2845,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2607,272 +2865,310 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>123537600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>114443400</v>
+      </c>
+      <c r="F57" s="3">
         <v>114224000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>108782900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>102111400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>89496700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>92592600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>89245200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>83526900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>83218000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>85769000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>82088800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>82664700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>85615600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>87493100</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7677200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>7890300</v>
+      </c>
+      <c r="F58" s="3">
         <v>7802400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>8305400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>9306700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>6649400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>6369100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5798800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>4747000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3828500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>6437400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>5886400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>5614700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>4956000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>3761900</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6943400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6142000</v>
+      </c>
+      <c r="F59" s="3">
         <v>6995000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5976300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>5596700</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
         <v>6221100</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>3008900</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>3055500</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>138196400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>128511700</v>
+      </c>
+      <c r="F60" s="3">
         <v>129332500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>123111700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>117066700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>96192600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>105465000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>95090500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>88321400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>87096200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>95633000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>88016400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>88324400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>90618100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>94676800</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9272300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>8640900</v>
+      </c>
+      <c r="F61" s="3">
         <v>8390200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>6766600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7029400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>5682300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5767500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>5586900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4827800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>4833200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>4616900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4253800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4437200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>4205300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3818800</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2037500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2133500</v>
+      </c>
+      <c r="F62" s="3">
         <v>504400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1733900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2031900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>5523000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>644900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>5114200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>4748300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>5049800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>840000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>4451300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>4752500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>5109200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>711300</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2915,8 +3211,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2959,8 +3261,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3003,52 +3311,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>150079200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>139803000</v>
+      </c>
+      <c r="F66" s="3">
         <v>138897400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>132089000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>126621900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>107839700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>112449300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>106228200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>98312900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>97472900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>101764900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>97218600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>98048600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>100479700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>99899300</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3065,8 +3385,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3109,8 +3431,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3153,8 +3481,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3197,8 +3531,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3241,52 +3581,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10198400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>9389000</v>
+      </c>
+      <c r="F72" s="3">
         <v>9141200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>8713700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>8359300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>7348200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>7314100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>6976000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>6668600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>6602900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>6528800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>5955400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>5992200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>5974400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>5798100</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3329,8 +3681,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3373,8 +3731,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3417,52 +3781,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11677400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>10817200</v>
+      </c>
+      <c r="F76" s="3">
         <v>10605100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>10130800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>9757200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8717600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8667300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8396100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8054200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>7971600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>7906600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>7241600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>7274500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>7269100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>7075600</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3505,57 +3881,69 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3598,8 +3986,14 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3616,52 +4010,60 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F83" s="3">
         <v>-40400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>47900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>44900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>46000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>-68600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>44300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>39600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>41800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>-63100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>40400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>40300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>43800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>-67500</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3704,8 +4106,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3748,8 +4156,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3792,8 +4206,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3836,8 +4256,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3880,52 +4306,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>991200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1521200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-133600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1266600</v>
       </c>
-      <c r="F89" s="3">
-        <v>801900</v>
-      </c>
-      <c r="G89" s="3">
-        <v>54500</v>
-      </c>
       <c r="H89" s="3">
+        <v>948900</v>
+      </c>
+      <c r="I89" s="3">
+        <v>54800</v>
+      </c>
+      <c r="J89" s="3">
         <v>619400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-166000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-51300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>754900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>951900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>263800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-530200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-126500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-189100</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3942,52 +4380,60 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-53400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-55700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-58700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-53800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-48100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-46700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-78800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-49500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-52100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-45800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-45500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-89400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-102600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-85800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-84200</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4030,8 +4476,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4074,52 +4526,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2995900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1040800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1803600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-2750100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-2768800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-2200100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1193500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-3075900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2733000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-172800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1944600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1624200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1128000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-3572400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1520100</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4136,52 +4600,60 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>299800</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3">
         <v>177500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>134700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>185800</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>93600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>84200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>83700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>49800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>33900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>93300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>102600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>52400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>50900</v>
       </c>
     </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4224,8 +4696,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4268,8 +4746,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4312,136 +4796,160 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>829400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1206400</v>
+      </c>
+      <c r="F100" s="3">
         <v>1786400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>3562000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>4214200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-737700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>2181900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>6163300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>2916500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1634100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-814200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>1545800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>779500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>1940900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-108100</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-220800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>17200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-80400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>20700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>30500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-93000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>31500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>38000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>8900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>223000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>7600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-17200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-24400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-54300</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1393000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3742800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-154300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>2054600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2173400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2865900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1527300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>2942200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>162800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1050100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1899900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>216800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-840600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1749000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1594300</v>
       </c>
     </row>
